--- a/artfynd/A 65181-2023 artfynd.xlsx
+++ b/artfynd/A 65181-2023 artfynd.xlsx
@@ -2412,11 +2412,11 @@
         <v>116869039</v>
       </c>
       <c r="B18" t="n">
-        <v>56491</v>
+        <v>56593</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">

--- a/artfynd/A 65181-2023 artfynd.xlsx
+++ b/artfynd/A 65181-2023 artfynd.xlsx
@@ -2412,11 +2412,11 @@
         <v>116869039</v>
       </c>
       <c r="B18" t="n">
-        <v>56593</v>
+        <v>56491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
